--- a/JP1/21_ドキュメント/【Win2016対応】JP1_インストールチェックリスト.xlsx
+++ b/JP1/21_ドキュメント/【Win2016対応】JP1_インストールチェックリスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tosa_git\proj-G-foot\JP1\21_ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tosa_git\proj_DHI_G-foot\JP1\21_ドキュメント\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466589DC-1F06-46EF-95C0-D84340F75836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069DAFED-D8A4-4511-89E4-5A15C4CC909B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{0D0C29E1-D373-4335-802D-B54E9CD6C8A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{0D0C29E1-D373-4335-802D-B54E9CD6C8A7}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="20" r:id="rId1"/>
@@ -3952,6 +3952,15 @@
     <xf numFmtId="49" fontId="9" fillId="10" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3970,25 +3979,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4003,6 +4018,18 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4010,33 +4037,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4389,7 +4389,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="224120" y="425265"/>
-          <a:ext cx="7313315" cy="6689698"/>
+          <a:ext cx="7380550" cy="6496957"/>
           <a:chOff x="219077" y="428627"/>
           <a:chExt cx="6563642" cy="6496957"/>
         </a:xfrm>
@@ -4569,8 +4569,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="224119" y="14099801"/>
-          <a:ext cx="11910547" cy="6195453"/>
+          <a:off x="224119" y="13718801"/>
+          <a:ext cx="12018124" cy="6020641"/>
           <a:chOff x="219076" y="13725525"/>
           <a:chExt cx="10717121" cy="6020641"/>
         </a:xfrm>
@@ -4689,8 +4689,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="224118" y="20720797"/>
-          <a:ext cx="11084008" cy="7678752"/>
+          <a:off x="224118" y="20156021"/>
+          <a:ext cx="11184861" cy="7459117"/>
           <a:chOff x="222250" y="20932775"/>
           <a:chExt cx="9875641" cy="7770267"/>
         </a:xfrm>
@@ -5344,8 +5344,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="248966" y="98794663"/>
-          <a:ext cx="11904752" cy="3128545"/>
+          <a:off x="248966" y="96080599"/>
+          <a:ext cx="12012329" cy="3038898"/>
           <a:chOff x="223630" y="95127417"/>
           <a:chExt cx="10756880" cy="2972637"/>
         </a:xfrm>
@@ -5560,8 +5560,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="257250" y="102432410"/>
-          <a:ext cx="10712482" cy="4127125"/>
+          <a:off x="257250" y="99619734"/>
+          <a:ext cx="10813335" cy="4010584"/>
           <a:chOff x="224118" y="103474557"/>
           <a:chExt cx="9535865" cy="4127126"/>
         </a:xfrm>
@@ -5680,8 +5680,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="224119" y="115018297"/>
-          <a:ext cx="11910547" cy="4022336"/>
+          <a:off x="224119" y="111855997"/>
+          <a:ext cx="12018124" cy="3905795"/>
           <a:chOff x="219076" y="114071400"/>
           <a:chExt cx="10717121" cy="3905795"/>
         </a:xfrm>
@@ -5800,8 +5800,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="224118" y="119433415"/>
-          <a:ext cx="11920074" cy="6218987"/>
+          <a:off x="224118" y="116150091"/>
+          <a:ext cx="12027651" cy="6039693"/>
           <a:chOff x="219075" y="117205125"/>
           <a:chExt cx="10726648" cy="6039693"/>
         </a:xfrm>
@@ -6066,8 +6066,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="224118" y="143580409"/>
-          <a:ext cx="11832851" cy="6320679"/>
+          <a:off x="224118" y="139638180"/>
+          <a:ext cx="11940428" cy="6141385"/>
           <a:chOff x="219075" y="141846299"/>
           <a:chExt cx="10639425" cy="5668166"/>
         </a:xfrm>
@@ -6781,8 +6781,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="264319" y="328611"/>
-          <a:ext cx="11956311" cy="6924401"/>
+          <a:off x="269081" y="326230"/>
+          <a:ext cx="11889636" cy="6648176"/>
           <a:chOff x="252413" y="197644"/>
           <a:chExt cx="11803123" cy="5391903"/>
         </a:xfrm>
@@ -6901,8 +6901,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="261937" y="8417718"/>
-          <a:ext cx="5737151" cy="7601692"/>
+          <a:off x="266699" y="8105774"/>
+          <a:ext cx="5713339" cy="7296892"/>
           <a:chOff x="273843" y="6036469"/>
           <a:chExt cx="5153745" cy="5315692"/>
         </a:xfrm>
@@ -7214,8 +7214,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="238125" y="56352280"/>
-          <a:ext cx="5710957" cy="7358801"/>
+          <a:off x="242887" y="54161530"/>
+          <a:ext cx="5687145" cy="7063526"/>
           <a:chOff x="238125" y="39659718"/>
           <a:chExt cx="5127551" cy="5144238"/>
         </a:xfrm>
@@ -7632,7 +7632,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="8">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -7655,12 +7655,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A885A04-837D-4A23-9E6F-1669AC5F7BEE}">
   <dimension ref="B2:AB33"/>
-  <sheetFormatPr defaultColWidth="4.125" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="4.09765625" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="16384" width="4.125" style="52"/>
+    <col min="1" max="16384" width="4.09765625" style="52"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:28" s="50" customFormat="1" ht="25.5">
+    <row r="2" spans="2:28" s="50" customFormat="1" ht="26.4">
       <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
@@ -7723,100 +7723,100 @@
       </c>
     </row>
     <row r="15" spans="2:28">
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86" t="s">
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="86"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="86"/>
-      <c r="R15" s="86"/>
-      <c r="S15" s="86"/>
-      <c r="T15" s="86"/>
-      <c r="U15" s="86"/>
-      <c r="V15" s="86"/>
-      <c r="W15" s="86"/>
-      <c r="X15" s="86"/>
-      <c r="Y15" s="86"/>
-      <c r="Z15" s="86"/>
-      <c r="AA15" s="86"/>
-      <c r="AB15" s="86"/>
-    </row>
-    <row r="16" spans="2:28" ht="39.950000000000003" customHeight="1">
-      <c r="C16" s="87" t="s">
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+      <c r="K15" s="89"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="89"/>
+      <c r="V15" s="89"/>
+      <c r="W15" s="89"/>
+      <c r="X15" s="89"/>
+      <c r="Y15" s="89"/>
+      <c r="Z15" s="89"/>
+      <c r="AA15" s="89"/>
+      <c r="AB15" s="89"/>
+    </row>
+    <row r="16" spans="2:28" ht="39.9" customHeight="1">
+      <c r="C16" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="91" t="s">
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="87"/>
-      <c r="N16" s="87"/>
-      <c r="O16" s="87"/>
-      <c r="P16" s="87"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="87"/>
-      <c r="S16" s="87"/>
-      <c r="T16" s="87"/>
-      <c r="U16" s="87"/>
-      <c r="V16" s="87"/>
-      <c r="W16" s="87"/>
-      <c r="X16" s="87"/>
-      <c r="Y16" s="87"/>
-      <c r="Z16" s="87"/>
-      <c r="AA16" s="87"/>
-      <c r="AB16" s="87"/>
-    </row>
-    <row r="17" spans="2:28" ht="39.950000000000003" customHeight="1">
-      <c r="C17" s="87" t="s">
+      <c r="I16" s="90"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="O16" s="90"/>
+      <c r="P16" s="90"/>
+      <c r="Q16" s="90"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="90"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="90"/>
+    </row>
+    <row r="17" spans="2:28" ht="39.9" customHeight="1">
+      <c r="C17" s="90" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="87"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="91" t="s">
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="I17" s="87"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="87"/>
-      <c r="N17" s="87"/>
-      <c r="O17" s="87"/>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="90"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
+      <c r="O17" s="90"/>
+      <c r="P17" s="90"/>
+      <c r="Q17" s="90"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="90"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="90"/>
+      <c r="X17" s="90"/>
+      <c r="Y17" s="90"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="90"/>
+      <c r="AB17" s="90"/>
     </row>
     <row r="20" spans="2:28">
       <c r="B20" s="51" t="s">
@@ -7839,31 +7839,31 @@
       </c>
       <c r="D24" s="60"/>
       <c r="E24" s="61"/>
-      <c r="F24" s="86" t="s">
+      <c r="F24" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="86"/>
-      <c r="H24" s="86"/>
-      <c r="I24" s="86"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="86"/>
-      <c r="M24" s="86"/>
-      <c r="N24" s="86"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="86"/>
-      <c r="R24" s="86"/>
-      <c r="S24" s="86"/>
-      <c r="T24" s="86"/>
-      <c r="U24" s="86"/>
-      <c r="V24" s="86"/>
-      <c r="W24" s="86"/>
-      <c r="X24" s="86"/>
-      <c r="Y24" s="86"/>
-      <c r="Z24" s="86"/>
-      <c r="AA24" s="86"/>
-      <c r="AB24" s="86"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="89"/>
+      <c r="P24" s="89"/>
+      <c r="Q24" s="89"/>
+      <c r="R24" s="89"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="89"/>
+      <c r="W24" s="89"/>
+      <c r="X24" s="89"/>
+      <c r="Y24" s="89"/>
+      <c r="Z24" s="89"/>
+      <c r="AA24" s="89"/>
+      <c r="AB24" s="89"/>
     </row>
     <row r="25" spans="2:28">
       <c r="C25" s="62" t="s">
@@ -7871,31 +7871,31 @@
       </c>
       <c r="D25" s="63"/>
       <c r="E25" s="64"/>
-      <c r="F25" s="88" t="s">
+      <c r="F25" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="89"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="89"/>
-      <c r="K25" s="89"/>
-      <c r="L25" s="89"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="89"/>
-      <c r="P25" s="89"/>
-      <c r="Q25" s="89"/>
-      <c r="R25" s="89"/>
-      <c r="S25" s="89"/>
-      <c r="T25" s="89"/>
-      <c r="U25" s="89"/>
-      <c r="V25" s="89"/>
-      <c r="W25" s="89"/>
-      <c r="X25" s="89"/>
-      <c r="Y25" s="89"/>
-      <c r="Z25" s="89"/>
-      <c r="AA25" s="89"/>
-      <c r="AB25" s="90"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="92"/>
+      <c r="O25" s="92"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="92"/>
+      <c r="S25" s="92"/>
+      <c r="T25" s="92"/>
+      <c r="U25" s="92"/>
+      <c r="V25" s="92"/>
+      <c r="W25" s="92"/>
+      <c r="X25" s="92"/>
+      <c r="Y25" s="92"/>
+      <c r="Z25" s="92"/>
+      <c r="AA25" s="92"/>
+      <c r="AB25" s="93"/>
     </row>
     <row r="26" spans="2:28">
       <c r="C26" s="62" t="s">
@@ -7903,31 +7903,31 @@
       </c>
       <c r="D26" s="63"/>
       <c r="E26" s="64"/>
-      <c r="F26" s="87" t="s">
+      <c r="F26" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="87"/>
-      <c r="N26" s="87"/>
-      <c r="O26" s="87"/>
-      <c r="P26" s="87"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="87"/>
-      <c r="S26" s="87"/>
-      <c r="T26" s="87"/>
-      <c r="U26" s="87"/>
-      <c r="V26" s="87"/>
-      <c r="W26" s="87"/>
-      <c r="X26" s="87"/>
-      <c r="Y26" s="87"/>
-      <c r="Z26" s="87"/>
-      <c r="AA26" s="87"/>
-      <c r="AB26" s="87"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="90"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
+      <c r="O26" s="90"/>
+      <c r="P26" s="90"/>
+      <c r="Q26" s="90"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
+      <c r="T26" s="90"/>
+      <c r="U26" s="90"/>
+      <c r="V26" s="90"/>
+      <c r="W26" s="90"/>
+      <c r="X26" s="90"/>
+      <c r="Y26" s="90"/>
+      <c r="Z26" s="90"/>
+      <c r="AA26" s="90"/>
+      <c r="AB26" s="90"/>
     </row>
     <row r="27" spans="2:28">
       <c r="C27" s="62" t="s">
@@ -7935,31 +7935,31 @@
       </c>
       <c r="D27" s="63"/>
       <c r="E27" s="64"/>
-      <c r="F27" s="87" t="s">
+      <c r="F27" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="87"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="87"/>
-      <c r="P27" s="87"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="87"/>
-      <c r="S27" s="87"/>
-      <c r="T27" s="87"/>
-      <c r="U27" s="87"/>
-      <c r="V27" s="87"/>
-      <c r="W27" s="87"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="87"/>
-      <c r="Z27" s="87"/>
-      <c r="AA27" s="87"/>
-      <c r="AB27" s="87"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="90"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="90"/>
     </row>
     <row r="28" spans="2:28">
       <c r="C28" s="62" t="s">
@@ -7967,31 +7967,31 @@
       </c>
       <c r="D28" s="63"/>
       <c r="E28" s="64"/>
-      <c r="F28" s="87" t="s">
+      <c r="F28" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="87"/>
-      <c r="K28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="87"/>
-      <c r="N28" s="87"/>
-      <c r="O28" s="87"/>
-      <c r="P28" s="87"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="87"/>
-      <c r="S28" s="87"/>
-      <c r="T28" s="87"/>
-      <c r="U28" s="87"/>
-      <c r="V28" s="87"/>
-      <c r="W28" s="87"/>
-      <c r="X28" s="87"/>
-      <c r="Y28" s="87"/>
-      <c r="Z28" s="87"/>
-      <c r="AA28" s="87"/>
-      <c r="AB28" s="87"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="90"/>
+      <c r="P28" s="90"/>
+      <c r="Q28" s="90"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="90"/>
+      <c r="V28" s="90"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="90"/>
+      <c r="Z28" s="90"/>
+      <c r="AA28" s="90"/>
+      <c r="AB28" s="90"/>
     </row>
     <row r="29" spans="2:28">
       <c r="C29" s="62" t="s">
@@ -7999,31 +7999,31 @@
       </c>
       <c r="D29" s="63"/>
       <c r="E29" s="64"/>
-      <c r="F29" s="87" t="s">
+      <c r="F29" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="87"/>
-      <c r="H29" s="87"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="87"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="87"/>
-      <c r="N29" s="87"/>
-      <c r="O29" s="87"/>
-      <c r="P29" s="87"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="87"/>
-      <c r="S29" s="87"/>
-      <c r="T29" s="87"/>
-      <c r="U29" s="87"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="87"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="87"/>
-      <c r="Z29" s="87"/>
-      <c r="AA29" s="87"/>
-      <c r="AB29" s="87"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="90"/>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="90"/>
+      <c r="Z29" s="90"/>
+      <c r="AA29" s="90"/>
+      <c r="AB29" s="90"/>
     </row>
     <row r="30" spans="2:28">
       <c r="C30" s="62" t="s">
@@ -8031,31 +8031,31 @@
       </c>
       <c r="D30" s="63"/>
       <c r="E30" s="64"/>
-      <c r="F30" s="87" t="s">
+      <c r="F30" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="87"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="87"/>
-      <c r="P30" s="87"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="87"/>
-      <c r="S30" s="87"/>
-      <c r="T30" s="87"/>
-      <c r="U30" s="87"/>
-      <c r="V30" s="87"/>
-      <c r="W30" s="87"/>
-      <c r="X30" s="87"/>
-      <c r="Y30" s="87"/>
-      <c r="Z30" s="87"/>
-      <c r="AA30" s="87"/>
-      <c r="AB30" s="87"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="90"/>
+      <c r="P30" s="90"/>
+      <c r="Q30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="90"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="90"/>
+      <c r="Z30" s="90"/>
+      <c r="AA30" s="90"/>
+      <c r="AB30" s="90"/>
     </row>
     <row r="31" spans="2:28">
       <c r="C31" s="62" t="s">
@@ -8063,31 +8063,31 @@
       </c>
       <c r="D31" s="63"/>
       <c r="E31" s="64"/>
-      <c r="F31" s="87" t="s">
+      <c r="F31" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="G31" s="87"/>
-      <c r="H31" s="87"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="87"/>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="87"/>
-      <c r="N31" s="87"/>
-      <c r="O31" s="87"/>
-      <c r="P31" s="87"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="87"/>
-      <c r="S31" s="87"/>
-      <c r="T31" s="87"/>
-      <c r="U31" s="87"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="87"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="87"/>
-      <c r="Z31" s="87"/>
-      <c r="AA31" s="87"/>
-      <c r="AB31" s="87"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="90"/>
+      <c r="O31" s="90"/>
+      <c r="P31" s="90"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="90"/>
+      <c r="T31" s="90"/>
+      <c r="U31" s="90"/>
+      <c r="V31" s="90"/>
+      <c r="W31" s="90"/>
+      <c r="X31" s="90"/>
+      <c r="Y31" s="90"/>
+      <c r="Z31" s="90"/>
+      <c r="AA31" s="90"/>
+      <c r="AB31" s="90"/>
     </row>
     <row r="32" spans="2:28">
       <c r="C32" s="62" t="s">
@@ -8095,31 +8095,31 @@
       </c>
       <c r="D32" s="63"/>
       <c r="E32" s="64"/>
-      <c r="F32" s="87" t="s">
+      <c r="F32" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="87"/>
-      <c r="H32" s="87"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="87"/>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="87"/>
-      <c r="N32" s="87"/>
-      <c r="O32" s="87"/>
-      <c r="P32" s="87"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="87"/>
-      <c r="S32" s="87"/>
-      <c r="T32" s="87"/>
-      <c r="U32" s="87"/>
-      <c r="V32" s="87"/>
-      <c r="W32" s="87"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="87"/>
-      <c r="AA32" s="87"/>
-      <c r="AB32" s="87"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="90"/>
+      <c r="O32" s="90"/>
+      <c r="P32" s="90"/>
+      <c r="Q32" s="90"/>
+      <c r="R32" s="90"/>
+      <c r="S32" s="90"/>
+      <c r="T32" s="90"/>
+      <c r="U32" s="90"/>
+      <c r="V32" s="90"/>
+      <c r="W32" s="90"/>
+      <c r="X32" s="90"/>
+      <c r="Y32" s="90"/>
+      <c r="Z32" s="90"/>
+      <c r="AA32" s="90"/>
+      <c r="AB32" s="90"/>
     </row>
     <row r="33" spans="3:28">
       <c r="C33" s="62" t="s">
@@ -8127,31 +8127,31 @@
       </c>
       <c r="D33" s="63"/>
       <c r="E33" s="64"/>
-      <c r="F33" s="87" t="s">
+      <c r="F33" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="87"/>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="87"/>
-      <c r="N33" s="87"/>
-      <c r="O33" s="87"/>
-      <c r="P33" s="87"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="87"/>
-      <c r="S33" s="87"/>
-      <c r="T33" s="87"/>
-      <c r="U33" s="87"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="87"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="87"/>
-      <c r="Z33" s="87"/>
-      <c r="AA33" s="87"/>
-      <c r="AB33" s="87"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="90"/>
+      <c r="M33" s="90"/>
+      <c r="N33" s="90"/>
+      <c r="O33" s="90"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="90"/>
+      <c r="R33" s="90"/>
+      <c r="S33" s="90"/>
+      <c r="T33" s="90"/>
+      <c r="U33" s="90"/>
+      <c r="V33" s="90"/>
+      <c r="W33" s="90"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="90"/>
+      <c r="Z33" s="90"/>
+      <c r="AA33" s="90"/>
+      <c r="AB33" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -8186,19 +8186,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H58"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="3.59765625" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="2" width="3.25" style="40" customWidth="1"/>
-    <col min="3" max="3" width="3.25" style="41" customWidth="1"/>
-    <col min="4" max="4" width="38.375" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="3.19921875" style="40" customWidth="1"/>
+    <col min="3" max="3" width="3.19921875" style="41" customWidth="1"/>
+    <col min="4" max="4" width="38.3984375" style="40" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="55.5" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.375" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.875" style="40" customWidth="1"/>
-    <col min="8" max="8" width="38.375" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="3.625" style="40"/>
+    <col min="6" max="6" width="38.3984375" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.8984375" style="40" customWidth="1"/>
+    <col min="8" max="8" width="38.3984375" style="40" customWidth="1"/>
+    <col min="9" max="16384" width="3.59765625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="16.8">
       <c r="A1" s="39" t="s">
         <v>192</v>
       </c>
@@ -8214,15 +8214,15 @@
       <c r="B4" s="39"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="101" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="93" t="s">
+      <c r="E5" s="101"/>
+      <c r="F5" s="102" t="s">
         <v>195</v>
       </c>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
     </row>
     <row r="6" spans="1:8">
       <c r="D6" s="42" t="s">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="1:8" ht="49.5">
+    <row r="9" spans="1:8" ht="48.6">
       <c r="D9" s="44" t="s">
         <v>40</v>
       </c>
@@ -8339,7 +8339,7 @@
     <row r="15" spans="1:8">
       <c r="B15" s="39"/>
     </row>
-    <row r="16" spans="1:8" ht="18.75">
+    <row r="16" spans="1:8" ht="18">
       <c r="C16" s="72" t="s">
         <v>203</v>
       </c>
@@ -8349,84 +8349,84 @@
       <c r="G16"/>
       <c r="H16"/>
     </row>
-    <row r="17" spans="3:8" ht="18.75">
+    <row r="17" spans="3:8" ht="18">
       <c r="C17"/>
       <c r="D17" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="94" t="s">
+      <c r="E17" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
       <c r="H17" s="73" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="3:8" ht="18.75">
+    <row r="18" spans="3:8" ht="18">
       <c r="C18"/>
       <c r="D18" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="98"/>
       <c r="H18" s="74" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="3:8" ht="33">
+    <row r="19" spans="3:8" ht="32.4">
       <c r="C19"/>
       <c r="D19" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="103" t="s">
         <v>210</v>
       </c>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
       <c r="H19" s="74" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="3:8" ht="18.75">
+    <row r="20" spans="3:8" ht="18">
       <c r="C20"/>
       <c r="D20" s="74" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="97" t="s">
+      <c r="E20" s="99" t="s">
         <v>213</v>
       </c>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
       <c r="H20" s="74" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="3:8" ht="18.75">
+    <row r="21" spans="3:8" ht="18">
       <c r="C21"/>
       <c r="D21" s="74" t="s">
         <v>215</v>
       </c>
-      <c r="E21" s="97" t="s">
+      <c r="E21" s="99" t="s">
         <v>216</v>
       </c>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
       <c r="H21" s="74" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="3:8" ht="18.75">
+    <row r="22" spans="3:8" ht="18">
       <c r="C22"/>
       <c r="D22" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="E22" s="97" t="s">
+      <c r="E22" s="99" t="s">
         <v>219</v>
       </c>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
       <c r="H22" s="74" t="s">
         <v>220</v>
       </c>
@@ -8436,28 +8436,28 @@
       <c r="D23" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="E23" s="98" t="s">
+      <c r="E23" s="97" t="s">
         <v>222</v>
       </c>
-      <c r="F23" s="98"/>
-      <c r="G23" s="98"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
       <c r="H23" s="74" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="3:8" ht="18.75">
+    <row r="24" spans="3:8" ht="18">
       <c r="C24"/>
       <c r="D24" s="74" t="s">
         <v>224</v>
       </c>
-      <c r="E24" s="97" t="s">
+      <c r="E24" s="99" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="97"/>
-      <c r="G24" s="97"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
       <c r="H24" s="74"/>
     </row>
-    <row r="25" spans="3:8" ht="18.75">
+    <row r="25" spans="3:8" ht="18">
       <c r="C25"/>
       <c r="D25"/>
       <c r="E25"/>
@@ -8465,7 +8465,7 @@
       <c r="G25"/>
       <c r="H25"/>
     </row>
-    <row r="26" spans="3:8" ht="18.75">
+    <row r="26" spans="3:8" ht="18">
       <c r="C26" s="72" t="s">
         <v>226</v>
       </c>
@@ -8475,70 +8475,70 @@
       <c r="G26"/>
       <c r="H26"/>
     </row>
-    <row r="27" spans="3:8" ht="18.75">
+    <row r="27" spans="3:8" ht="18">
       <c r="C27"/>
       <c r="D27" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="E27" s="94" t="s">
+      <c r="E27" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="100"/>
       <c r="H27" s="73" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="28" spans="3:8" ht="18.75">
+    <row r="28" spans="3:8" ht="18">
       <c r="C28"/>
       <c r="D28" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="E28" s="95"/>
-      <c r="F28" s="95"/>
-      <c r="G28" s="95"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98"/>
       <c r="H28" s="74" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="3:8" ht="49.5">
+    <row r="29" spans="3:8" ht="48.6">
       <c r="C29"/>
       <c r="D29" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="E29" s="98" t="s">
+      <c r="E29" s="97" t="s">
         <v>273</v>
       </c>
-      <c r="F29" s="98"/>
-      <c r="G29" s="98"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
       <c r="H29" s="74" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="30" spans="3:8" ht="18.75">
+    <row r="30" spans="3:8" ht="18">
       <c r="C30"/>
       <c r="D30" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="E30" s="97" t="s">
+      <c r="E30" s="99" t="s">
         <v>228</v>
       </c>
-      <c r="F30" s="97"/>
-      <c r="G30" s="97"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
       <c r="H30" s="74" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="3:8" ht="18.75">
+    <row r="31" spans="3:8" ht="18">
       <c r="C31"/>
       <c r="D31" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="E31" s="98" t="s">
+      <c r="E31" s="97" t="s">
         <v>231</v>
       </c>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
       <c r="H31" s="74" t="s">
         <v>211</v>
       </c>
@@ -8548,44 +8548,44 @@
       <c r="D32" s="74" t="s">
         <v>232</v>
       </c>
-      <c r="E32" s="98" t="s">
+      <c r="E32" s="97" t="s">
         <v>233</v>
       </c>
-      <c r="F32" s="98"/>
-      <c r="G32" s="98"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
       <c r="H32" s="74" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="33" spans="3:8" ht="18.75">
+    <row r="33" spans="3:8" ht="18">
       <c r="C33"/>
       <c r="D33" s="74" t="s">
         <v>235</v>
       </c>
-      <c r="E33" s="97" t="s">
+      <c r="E33" s="99" t="s">
         <v>236</v>
       </c>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
       <c r="H33" s="74" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="34" spans="3:8" ht="18.75">
+    <row r="34" spans="3:8" ht="18">
       <c r="C34"/>
       <c r="D34" s="74" t="s">
         <v>238</v>
       </c>
-      <c r="E34" s="97" t="s">
+      <c r="E34" s="99" t="s">
         <v>239</v>
       </c>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
       <c r="H34" s="74" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="35" spans="3:8" ht="18.75">
+    <row r="35" spans="3:8" ht="18">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -8593,7 +8593,7 @@
       <c r="G35"/>
       <c r="H35"/>
     </row>
-    <row r="36" spans="3:8" ht="18.75">
+    <row r="36" spans="3:8" ht="18">
       <c r="C36" s="72" t="s">
         <v>241</v>
       </c>
@@ -8603,54 +8603,54 @@
       <c r="G36"/>
       <c r="H36"/>
     </row>
-    <row r="37" spans="3:8" ht="18.75">
+    <row r="37" spans="3:8" ht="18">
       <c r="C37"/>
       <c r="D37" s="73" t="s">
         <v>204</v>
       </c>
-      <c r="E37" s="94" t="s">
+      <c r="E37" s="100" t="s">
         <v>205</v>
       </c>
-      <c r="F37" s="94"/>
-      <c r="G37" s="94"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="100"/>
       <c r="H37" s="73" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="38" spans="3:8" ht="18.75">
+    <row r="38" spans="3:8" ht="18">
       <c r="C38"/>
       <c r="D38" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="E38" s="95"/>
-      <c r="F38" s="95"/>
-      <c r="G38" s="95"/>
+      <c r="E38" s="98"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="98"/>
       <c r="H38" s="74" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="39" spans="3:8" ht="33">
+    <row r="39" spans="3:8" ht="32.4">
       <c r="C39"/>
       <c r="D39" s="74" t="s">
         <v>209</v>
       </c>
-      <c r="E39" s="98" t="s">
+      <c r="E39" s="97" t="s">
         <v>275</v>
       </c>
-      <c r="F39" s="98"/>
-      <c r="G39" s="98"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97"/>
       <c r="H39" s="74" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="40" spans="3:8" ht="18.75">
+    <row r="40" spans="3:8" ht="18">
       <c r="C40"/>
       <c r="D40" s="74" t="s">
         <v>243</v>
       </c>
-      <c r="E40" s="95"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="98"/>
       <c r="H40" s="74" t="s">
         <v>244</v>
       </c>
@@ -8660,209 +8660,212 @@
       <c r="D41" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="E41" s="98" t="s">
+      <c r="E41" s="97" t="s">
         <v>233</v>
       </c>
-      <c r="F41" s="98"/>
-      <c r="G41" s="98"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97"/>
       <c r="H41" s="74" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="42" spans="3:8" ht="18.75">
+    <row r="42" spans="3:8" ht="18">
       <c r="C42"/>
       <c r="D42" s="74" t="s">
         <v>247</v>
       </c>
-      <c r="E42" s="97" t="s">
+      <c r="E42" s="99" t="s">
         <v>216</v>
       </c>
-      <c r="F42" s="97"/>
-      <c r="G42" s="97"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99"/>
       <c r="H42" s="74" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="44" spans="3:8" ht="18.75" customHeight="1">
-      <c r="C44" s="107" t="s">
+      <c r="C44" s="86" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="45" spans="3:8">
-      <c r="D45" s="108" t="s">
+      <c r="D45" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="E45" s="109" t="s">
+      <c r="E45" s="96" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="109"/>
-      <c r="G45" s="109"/>
-      <c r="H45" s="108" t="s">
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="87" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="46" spans="3:8">
-      <c r="D46" s="110" t="s">
+      <c r="D46" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="E46" s="111" t="s">
+      <c r="E46" s="95" t="s">
         <v>318</v>
       </c>
-      <c r="F46" s="111"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="110" t="s">
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="88" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="47" spans="3:8">
-      <c r="D47" s="110" t="s">
+      <c r="D47" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="E47" s="111" t="s">
+      <c r="E47" s="95" t="s">
         <v>320</v>
       </c>
-      <c r="F47" s="111"/>
-      <c r="G47" s="111"/>
-      <c r="H47" s="110" t="s">
+      <c r="F47" s="95"/>
+      <c r="G47" s="95"/>
+      <c r="H47" s="88" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="48" spans="3:8">
-      <c r="D48" s="110" t="s">
+      <c r="D48" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="E48" s="111" t="s">
+      <c r="E48" s="95" t="s">
         <v>322</v>
       </c>
-      <c r="F48" s="111"/>
-      <c r="G48" s="111"/>
-      <c r="H48" s="110" t="s">
+      <c r="F48" s="95"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="88" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="49" spans="3:8">
-      <c r="D49" s="110" t="s">
+      <c r="D49" s="88" t="s">
         <v>324</v>
       </c>
-      <c r="E49" s="111" t="s">
+      <c r="E49" s="95" t="s">
         <v>325</v>
       </c>
-      <c r="F49" s="111"/>
-      <c r="G49" s="111"/>
-      <c r="H49" s="110" t="s">
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="88" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="50" spans="3:8">
-      <c r="D50" s="110" t="s">
+      <c r="D50" s="88" t="s">
         <v>327</v>
       </c>
-      <c r="E50" s="111" t="s">
+      <c r="E50" s="95" t="s">
         <v>328</v>
       </c>
-      <c r="F50" s="111"/>
-      <c r="G50" s="111"/>
-      <c r="H50" s="110" t="s">
+      <c r="F50" s="95"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="88" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="52" spans="3:8" ht="18.75" customHeight="1">
-      <c r="C52" s="107" t="s">
+      <c r="C52" s="86" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="53" spans="3:8">
-      <c r="D53" s="108" t="s">
+      <c r="D53" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="E53" s="109" t="s">
+      <c r="E53" s="96" t="s">
         <v>205</v>
       </c>
-      <c r="F53" s="109"/>
-      <c r="G53" s="109"/>
-      <c r="H53" s="108" t="s">
+      <c r="F53" s="96"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="87" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="54" spans="3:8">
-      <c r="D54" s="110" t="s">
+      <c r="D54" s="88" t="s">
         <v>207</v>
       </c>
-      <c r="E54" s="111" t="s">
+      <c r="E54" s="95" t="s">
         <v>318</v>
       </c>
-      <c r="F54" s="111"/>
-      <c r="G54" s="111"/>
-      <c r="H54" s="110" t="s">
+      <c r="F54" s="95"/>
+      <c r="G54" s="95"/>
+      <c r="H54" s="88" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="55" spans="3:8">
-      <c r="D55" s="110" t="s">
+      <c r="D55" s="88" t="s">
         <v>209</v>
       </c>
-      <c r="E55" s="111" t="s">
+      <c r="E55" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="F55" s="111"/>
-      <c r="G55" s="111"/>
-      <c r="H55" s="110" t="s">
+      <c r="F55" s="95"/>
+      <c r="G55" s="95"/>
+      <c r="H55" s="88" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="56" spans="3:8">
-      <c r="D56" s="110" t="s">
+      <c r="D56" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="E56" s="111" t="s">
+      <c r="E56" s="95" t="s">
         <v>322</v>
       </c>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="110" t="s">
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="88" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="57" spans="3:8">
-      <c r="D57" s="110" t="s">
+      <c r="D57" s="88" t="s">
         <v>335</v>
       </c>
-      <c r="E57" s="111" t="s">
+      <c r="E57" s="95" t="s">
         <v>336</v>
       </c>
-      <c r="F57" s="111"/>
-      <c r="G57" s="111"/>
-      <c r="H57" s="110" t="s">
+      <c r="F57" s="95"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="88" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="58" spans="3:8">
-      <c r="D58" s="110" t="s">
+      <c r="D58" s="88" t="s">
         <v>327</v>
       </c>
-      <c r="E58" s="111" t="s">
+      <c r="E58" s="95" t="s">
         <v>338</v>
       </c>
-      <c r="F58" s="111"/>
-      <c r="G58" s="111"/>
-      <c r="H58" s="110" t="s">
+      <c r="F58" s="95"/>
+      <c r="G58" s="95"/>
+      <c r="H58" s="88" t="s">
         <v>339</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="E31:G31"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="E40:G40"/>
     <mergeCell ref="E41:G41"/>
@@ -8872,21 +8875,18 @@
     <mergeCell ref="E34:G34"/>
     <mergeCell ref="E37:G37"/>
     <mergeCell ref="E38:G38"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="E56:G56"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.19685039370078741"/>
@@ -8901,22 +8901,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9048CCEC-93A2-43D9-B8C0-B7E8F5289D53}">
   <dimension ref="A2:M51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="2" width="3.625" style="47" customWidth="1"/>
-    <col min="3" max="3" width="5.375" style="47" customWidth="1"/>
+    <col min="1" max="2" width="3.59765625" style="47" customWidth="1"/>
+    <col min="3" max="3" width="5.3984375" style="47" customWidth="1"/>
     <col min="4" max="4" width="25" style="47" customWidth="1"/>
     <col min="5" max="5" width="17.5" style="47" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="27.5" style="47" customWidth="1"/>
     <col min="7" max="7" width="50" style="47" customWidth="1"/>
-    <col min="8" max="8" width="10.875" style="47" customWidth="1"/>
+    <col min="8" max="8" width="10.8984375" style="47" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="47" customWidth="1"/>
-    <col min="10" max="10" width="10.875" style="47" customWidth="1"/>
+    <col min="10" max="10" width="10.8984375" style="47" customWidth="1"/>
     <col min="11" max="11" width="35" style="47" customWidth="1"/>
     <col min="12" max="16384" width="9" style="47"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" s="46" customFormat="1" ht="24.75">
+    <row r="2" spans="1:13" s="46" customFormat="1" ht="26.4">
       <c r="A2" s="45"/>
       <c r="B2" s="48" t="s">
         <v>202</v>
@@ -8924,30 +8924,30 @@
       <c r="C2" s="45"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="C3" s="102" t="s">
+      <c r="C3" s="107" t="s">
         <v>361</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75">
-      <c r="C4" s="99" t="s">
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+    </row>
+    <row r="4" spans="1:13" ht="17.399999999999999">
+      <c r="C4" s="104" t="s">
         <v>278</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
     </row>
     <row r="5" spans="1:13">
       <c r="C5" s="75" t="s">
@@ -8978,7 +8978,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="66">
+    <row r="6" spans="1:13" ht="64.8">
       <c r="C6" s="77">
         <v>1</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="66">
+    <row r="7" spans="1:13" ht="81">
       <c r="C7" s="77">
         <v>2</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="132">
+    <row r="8" spans="1:13" ht="145.80000000000001">
       <c r="C8" s="77">
         <v>3</v>
       </c>
@@ -9048,7 +9048,7 @@
       </c>
       <c r="M8" s="68"/>
     </row>
-    <row r="9" spans="1:13" ht="82.5">
+    <row r="9" spans="1:13" ht="81">
       <c r="C9" s="77">
         <v>4</v>
       </c>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="M9" s="82"/>
     </row>
-    <row r="10" spans="1:13" ht="18.75">
+    <row r="10" spans="1:13" ht="18">
       <c r="C10" s="80"/>
       <c r="D10" s="80"/>
       <c r="E10" s="80"/>
@@ -9083,18 +9083,18 @@
       <c r="J10" s="80"/>
       <c r="K10" s="80"/>
     </row>
-    <row r="11" spans="1:13" ht="18.75">
-      <c r="C11" s="99" t="s">
+    <row r="11" spans="1:13" ht="17.399999999999999">
+      <c r="C11" s="104" t="s">
         <v>293</v>
       </c>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
     </row>
     <row r="12" spans="1:13">
       <c r="C12" s="75" t="s">
@@ -9125,7 +9125,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="115.5">
+    <row r="13" spans="1:13" ht="113.4">
       <c r="C13" s="77">
         <v>1</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="99">
+    <row r="14" spans="1:13" ht="97.2">
       <c r="C14" s="77">
         <v>2</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="49.5">
+    <row r="15" spans="1:13" ht="48.6">
       <c r="C15" s="77">
         <v>3</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="82.5">
+    <row r="16" spans="1:13" ht="97.2">
       <c r="C16" s="77">
         <v>4</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="3:11" ht="18.75">
+    <row r="17" spans="3:11" ht="18">
       <c r="C17" s="80"/>
       <c r="D17" s="80"/>
       <c r="E17" s="80"/>
@@ -9228,18 +9228,18 @@
       <c r="J17" s="80"/>
       <c r="K17" s="80"/>
     </row>
-    <row r="18" spans="3:11" ht="18.75">
-      <c r="C18" s="99" t="s">
+    <row r="18" spans="3:11" ht="17.399999999999999">
+      <c r="C18" s="104" t="s">
         <v>299</v>
       </c>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
-      <c r="J18" s="99"/>
-      <c r="K18" s="99"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
     </row>
     <row r="19" spans="3:11">
       <c r="C19" s="75" t="s">
@@ -9270,7 +9270,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="3:11" ht="99">
+    <row r="20" spans="3:11" ht="97.2">
       <c r="C20" s="77">
         <v>1</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="21" spans="3:11" ht="82.5">
+    <row r="21" spans="3:11" ht="81">
       <c r="C21" s="77">
         <v>2</v>
       </c>
@@ -9316,7 +9316,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22" spans="3:11" ht="18.75">
+    <row r="22" spans="3:11" ht="18">
       <c r="C22" s="80"/>
       <c r="D22" s="80"/>
       <c r="E22" s="80"/>
@@ -9327,18 +9327,18 @@
       <c r="J22" s="80"/>
       <c r="K22" s="80"/>
     </row>
-    <row r="23" spans="3:11" ht="18.75">
-      <c r="C23" s="112" t="s">
+    <row r="23" spans="3:11" ht="18">
+      <c r="C23" s="108" t="s">
         <v>340</v>
       </c>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="114"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="109"/>
+      <c r="I23" s="109"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="110"/>
     </row>
     <row r="24" spans="3:11">
       <c r="C24" s="75" t="s">
@@ -9438,7 +9438,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="28" spans="3:11" ht="18.75">
+    <row r="28" spans="3:11" ht="18">
       <c r="C28" s="80"/>
       <c r="D28" s="80"/>
       <c r="E28" s="80"/>
@@ -9449,18 +9449,18 @@
       <c r="J28" s="80"/>
       <c r="K28" s="80"/>
     </row>
-    <row r="29" spans="3:11" ht="18.75">
-      <c r="C29" s="112" t="s">
+    <row r="29" spans="3:11" ht="18">
+      <c r="C29" s="108" t="s">
         <v>351</v>
       </c>
-      <c r="D29" s="113"/>
-      <c r="E29" s="113"/>
-      <c r="F29" s="113"/>
-      <c r="G29" s="113"/>
-      <c r="H29" s="113"/>
-      <c r="I29" s="113"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="114"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="110"/>
     </row>
     <row r="30" spans="3:11">
       <c r="C30" s="75" t="s">
@@ -9514,7 +9514,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="32" spans="3:11" ht="129.94999999999999" customHeight="1">
+    <row r="32" spans="3:11" ht="129.9" customHeight="1">
       <c r="C32" s="77">
         <v>2</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="33" spans="3:11" ht="18.75">
+    <row r="33" spans="3:11" ht="18">
       <c r="C33" s="80"/>
       <c r="D33" s="80"/>
       <c r="E33" s="80"/>
@@ -9548,35 +9548,35 @@
       <c r="J33" s="80"/>
       <c r="K33" s="80"/>
     </row>
-    <row r="34" spans="3:11" ht="18.75">
-      <c r="C34" s="100" t="s">
+    <row r="34" spans="3:11" ht="17.399999999999999">
+      <c r="C34" s="105" t="s">
         <v>305</v>
       </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="100"/>
-      <c r="K34" s="100"/>
-    </row>
-    <row r="35" spans="3:11" ht="49.5">
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+    </row>
+    <row r="35" spans="3:11" ht="48.6">
       <c r="C35" s="81" t="s">
         <v>306</v>
       </c>
-      <c r="D35" s="101" t="s">
+      <c r="D35" s="106" t="s">
         <v>308</v>
       </c>
-      <c r="E35" s="101"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="101"/>
-      <c r="I35" s="101"/>
-      <c r="J35" s="101"/>
-      <c r="K35" s="101"/>
-    </row>
-    <row r="36" spans="3:11" ht="18.75">
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="106"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+      <c r="K35" s="106"/>
+    </row>
+    <row r="36" spans="3:11" ht="18">
       <c r="C36"/>
       <c r="D36"/>
       <c r="E36"/>
@@ -9587,7 +9587,7 @@
       <c r="J36"/>
       <c r="K36"/>
     </row>
-    <row r="37" spans="3:11" ht="18.75">
+    <row r="37" spans="3:11" ht="18">
       <c r="C37"/>
       <c r="D37"/>
       <c r="E37"/>
@@ -9598,7 +9598,7 @@
       <c r="J37"/>
       <c r="K37"/>
     </row>
-    <row r="38" spans="3:11" ht="18.75">
+    <row r="38" spans="3:11" ht="18">
       <c r="C38"/>
       <c r="D38"/>
       <c r="E38"/>
@@ -9609,7 +9609,7 @@
       <c r="J38"/>
       <c r="K38"/>
     </row>
-    <row r="39" spans="3:11" ht="18.75">
+    <row r="39" spans="3:11" ht="18">
       <c r="C39"/>
       <c r="D39"/>
       <c r="E39"/>
@@ -9620,7 +9620,7 @@
       <c r="J39"/>
       <c r="K39"/>
     </row>
-    <row r="40" spans="3:11" ht="18.75">
+    <row r="40" spans="3:11" ht="18">
       <c r="C40"/>
       <c r="D40"/>
       <c r="E40"/>
@@ -9631,7 +9631,7 @@
       <c r="J40"/>
       <c r="K40"/>
     </row>
-    <row r="41" spans="3:11" ht="18.75">
+    <row r="41" spans="3:11" ht="18">
       <c r="C41"/>
       <c r="D41"/>
       <c r="E41"/>
@@ -9642,7 +9642,7 @@
       <c r="J41"/>
       <c r="K41"/>
     </row>
-    <row r="42" spans="3:11" ht="18.75">
+    <row r="42" spans="3:11" ht="18">
       <c r="C42"/>
       <c r="D42"/>
       <c r="E42"/>
@@ -9653,7 +9653,7 @@
       <c r="J42"/>
       <c r="K42"/>
     </row>
-    <row r="43" spans="3:11" ht="18.75">
+    <row r="43" spans="3:11" ht="18">
       <c r="C43"/>
       <c r="D43"/>
       <c r="E43"/>
@@ -9664,7 +9664,7 @@
       <c r="J43"/>
       <c r="K43"/>
     </row>
-    <row r="44" spans="3:11" ht="18.75">
+    <row r="44" spans="3:11" ht="18">
       <c r="C44"/>
       <c r="D44"/>
       <c r="E44"/>
@@ -9675,7 +9675,7 @@
       <c r="J44"/>
       <c r="K44"/>
     </row>
-    <row r="45" spans="3:11" ht="18.75">
+    <row r="45" spans="3:11" ht="18">
       <c r="C45"/>
       <c r="D45"/>
       <c r="E45"/>
@@ -9686,7 +9686,7 @@
       <c r="J45"/>
       <c r="K45"/>
     </row>
-    <row r="46" spans="3:11" ht="18.75">
+    <row r="46" spans="3:11" ht="18">
       <c r="C46"/>
       <c r="D46"/>
       <c r="E46"/>
@@ -9697,7 +9697,7 @@
       <c r="J46"/>
       <c r="K46"/>
     </row>
-    <row r="47" spans="3:11" ht="18.75">
+    <row r="47" spans="3:11" ht="18">
       <c r="C47"/>
       <c r="D47"/>
       <c r="E47"/>
@@ -9708,7 +9708,7 @@
       <c r="J47"/>
       <c r="K47"/>
     </row>
-    <row r="48" spans="3:11" ht="18.75">
+    <row r="48" spans="3:11" ht="18">
       <c r="C48"/>
       <c r="D48"/>
       <c r="E48"/>
@@ -9719,7 +9719,7 @@
       <c r="J48"/>
       <c r="K48"/>
     </row>
-    <row r="49" spans="3:11" ht="18.75">
+    <row r="49" spans="3:11" ht="18">
       <c r="C49"/>
       <c r="D49"/>
       <c r="E49"/>
@@ -9730,7 +9730,7 @@
       <c r="J49"/>
       <c r="K49"/>
     </row>
-    <row r="50" spans="3:11" ht="18.75">
+    <row r="50" spans="3:11" ht="18">
       <c r="C50"/>
       <c r="D50"/>
       <c r="E50"/>
@@ -9741,7 +9741,7 @@
       <c r="J50"/>
       <c r="K50"/>
     </row>
-    <row r="51" spans="3:11" ht="18.75">
+    <row r="51" spans="3:11" ht="18">
       <c r="C51"/>
       <c r="D51"/>
       <c r="E51"/>
@@ -9778,16 +9778,16 @@
   <dimension ref="A1:O949"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="3" width="2.875" style="3" customWidth="1"/>
+    <col min="1" max="3" width="2.8984375" style="3" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="14.25">
+    <row r="1" spans="1:2" s="2" customFormat="1" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="14.25">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="14.4">
       <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
@@ -9836,7 +9836,7 @@
     <row r="44" spans="2:2" s="2" customFormat="1"/>
     <row r="45" spans="2:2" s="2" customFormat="1"/>
     <row r="46" spans="2:2" s="2" customFormat="1"/>
-    <row r="47" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="47" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B47" s="1" t="s">
         <v>47</v>
       </c>
@@ -9882,7 +9882,7 @@
     <row r="86" spans="2:2" s="2" customFormat="1"/>
     <row r="87" spans="2:2" s="2" customFormat="1"/>
     <row r="88" spans="2:2" s="2" customFormat="1"/>
-    <row r="89" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="89" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B89" s="1" t="s">
         <v>48</v>
       </c>
@@ -9928,7 +9928,7 @@
     <row r="128" s="2" customFormat="1"/>
     <row r="129" spans="2:2" s="2" customFormat="1"/>
     <row r="130" spans="2:2" s="2" customFormat="1"/>
-    <row r="131" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="131" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B131" s="1" t="s">
         <v>49</v>
       </c>
@@ -9983,7 +9983,7 @@
     <row r="179" spans="2:2" s="2" customFormat="1"/>
     <row r="180" spans="2:2" s="2" customFormat="1"/>
     <row r="181" spans="2:2" s="2" customFormat="1"/>
-    <row r="182" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="182" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B182" s="1" t="s">
         <v>50</v>
       </c>
@@ -10039,7 +10039,7 @@
     <row r="231" spans="2:2" s="2" customFormat="1"/>
     <row r="232" spans="2:2" s="2" customFormat="1"/>
     <row r="233" spans="2:2" s="2" customFormat="1"/>
-    <row r="234" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="234" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B234" s="1" t="s">
         <v>51</v>
       </c>
@@ -10080,7 +10080,7 @@
     <row r="268" spans="2:2" s="2" customFormat="1"/>
     <row r="269" spans="2:2" s="2" customFormat="1"/>
     <row r="270" spans="2:2" s="2" customFormat="1"/>
-    <row r="271" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="271" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B271" s="1" t="s">
         <v>52</v>
       </c>
@@ -10121,7 +10121,7 @@
     <row r="305" spans="2:2" s="2" customFormat="1"/>
     <row r="306" spans="2:2" s="2" customFormat="1"/>
     <row r="307" spans="2:2" s="2" customFormat="1"/>
-    <row r="308" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="308" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B308" s="1" t="s">
         <v>53</v>
       </c>
@@ -10162,7 +10162,7 @@
     <row r="342" spans="2:2" s="2" customFormat="1"/>
     <row r="343" spans="2:2" s="2" customFormat="1"/>
     <row r="344" spans="2:2" s="2" customFormat="1"/>
-    <row r="345" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="345" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B345" s="1" t="s">
         <v>54</v>
       </c>
@@ -10203,7 +10203,7 @@
     <row r="379" spans="2:2" s="2" customFormat="1"/>
     <row r="380" spans="2:2" s="2" customFormat="1"/>
     <row r="381" spans="2:2" s="2" customFormat="1"/>
-    <row r="382" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="382" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B382" s="1" t="s">
         <v>55</v>
       </c>
@@ -10217,7 +10217,7 @@
     <row r="389" spans="15:15" s="2" customFormat="1"/>
     <row r="390" spans="15:15" s="2" customFormat="1"/>
     <row r="391" spans="15:15" s="2" customFormat="1"/>
-    <row r="392" spans="15:15" s="2" customFormat="1" ht="16.5">
+    <row r="392" spans="15:15" s="2" customFormat="1" ht="16.2">
       <c r="O392" s="38"/>
     </row>
     <row r="393" spans="15:15" s="2" customFormat="1"/>
@@ -10246,21 +10246,21 @@
     <row r="416" s="2" customFormat="1"/>
     <row r="417" spans="1:3" s="2" customFormat="1"/>
     <row r="418" spans="1:3" s="2" customFormat="1"/>
-    <row r="419" spans="1:3" s="2" customFormat="1" ht="14.25">
+    <row r="419" spans="1:3" s="2" customFormat="1" ht="14.4">
       <c r="A419" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
     </row>
-    <row r="420" spans="1:3" s="2" customFormat="1" ht="14.25">
+    <row r="420" spans="1:3" s="2" customFormat="1" ht="14.4">
       <c r="A420" s="1"/>
       <c r="B420" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C420" s="1"/>
     </row>
-    <row r="421" spans="1:3" s="2" customFormat="1" ht="14.25">
+    <row r="421" spans="1:3" s="2" customFormat="1" ht="14.4">
       <c r="A421" s="1"/>
       <c r="B421" s="1" t="s">
         <v>58</v>
@@ -10308,7 +10308,7 @@
     <row r="460" spans="2:2" s="2" customFormat="1"/>
     <row r="461" spans="2:2" s="2" customFormat="1"/>
     <row r="462" spans="2:2" s="2" customFormat="1"/>
-    <row r="463" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="463" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B463" s="1" t="s">
         <v>59</v>
       </c>
@@ -10335,7 +10335,7 @@
     <row r="483" spans="2:2" s="2" customFormat="1"/>
     <row r="484" spans="2:2" s="2" customFormat="1"/>
     <row r="485" spans="2:2" s="2" customFormat="1"/>
-    <row r="486" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="486" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B486" s="1" t="s">
         <v>60</v>
       </c>
@@ -10370,28 +10370,28 @@
     <row r="514" spans="2:4" s="2" customFormat="1"/>
     <row r="515" spans="2:4" s="2" customFormat="1"/>
     <row r="516" spans="2:4" s="2" customFormat="1"/>
-    <row r="517" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="517" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B517" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
     </row>
-    <row r="518" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="518" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B518" s="1"/>
       <c r="C518" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D518" s="1"/>
     </row>
-    <row r="519" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="519" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B519" s="1"/>
       <c r="C519" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D519" s="1"/>
     </row>
-    <row r="520" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="520" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B520" s="1"/>
       <c r="C520" s="1" t="s">
         <v>64</v>
@@ -10503,7 +10503,7 @@
     <row r="623" s="2" customFormat="1"/>
     <row r="624" s="2" customFormat="1"/>
     <row r="625" spans="2:2" s="2" customFormat="1"/>
-    <row r="626" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="626" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B626" s="1" t="s">
         <v>65</v>
       </c>
@@ -10530,7 +10530,7 @@
     <row r="646" spans="2:2" s="2" customFormat="1"/>
     <row r="647" spans="2:2" s="2" customFormat="1"/>
     <row r="648" spans="2:2" s="2" customFormat="1"/>
-    <row r="649" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="649" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B649" s="1" t="s">
         <v>66</v>
       </c>
@@ -10613,14 +10613,14 @@
     <row r="725" spans="1:3" s="2" customFormat="1"/>
     <row r="726" spans="1:3" s="2" customFormat="1"/>
     <row r="727" spans="1:3" s="2" customFormat="1"/>
-    <row r="728" spans="1:3" s="2" customFormat="1" ht="14.25">
+    <row r="728" spans="1:3" s="2" customFormat="1" ht="14.4">
       <c r="A728" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
     </row>
-    <row r="729" spans="1:3" s="2" customFormat="1" ht="14.25">
+    <row r="729" spans="1:3" s="2" customFormat="1" ht="14.4">
       <c r="A729" s="1"/>
       <c r="B729" s="1" t="s">
         <v>68</v>
@@ -10654,7 +10654,7 @@
     <row r="754" spans="2:2" s="2" customFormat="1"/>
     <row r="755" spans="2:2" s="2" customFormat="1"/>
     <row r="756" spans="2:2" s="2" customFormat="1"/>
-    <row r="757" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="757" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B757" s="1" t="s">
         <v>69</v>
       </c>
@@ -10700,7 +10700,7 @@
     <row r="796" spans="2:2" s="2" customFormat="1"/>
     <row r="797" spans="2:2" s="2" customFormat="1"/>
     <row r="798" spans="2:2" s="2" customFormat="1"/>
-    <row r="799" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="799" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B799" s="1" t="s">
         <v>70</v>
       </c>
@@ -10778,28 +10778,28 @@
     <row r="870" spans="2:4" s="2" customFormat="1"/>
     <row r="871" spans="2:4" s="2" customFormat="1"/>
     <row r="872" spans="2:4" s="2" customFormat="1"/>
-    <row r="873" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="873" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B873" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C873" s="1"/>
       <c r="D873" s="1"/>
     </row>
-    <row r="874" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="874" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B874" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C874" s="1"/>
       <c r="D874" s="1"/>
     </row>
-    <row r="875" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="875" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B875" s="1"/>
       <c r="C875" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D875" s="1"/>
     </row>
-    <row r="876" spans="2:4" s="2" customFormat="1" ht="14.25">
+    <row r="876" spans="2:4" s="2" customFormat="1" ht="14.4">
       <c r="B876" s="1"/>
       <c r="C876" s="1" t="s">
         <v>63</v>
@@ -10839,7 +10839,7 @@
     <row r="907" spans="2:2" s="2" customFormat="1"/>
     <row r="908" spans="2:2" s="2" customFormat="1"/>
     <row r="909" spans="2:2" s="2" customFormat="1"/>
-    <row r="910" spans="2:2" s="2" customFormat="1" ht="14.25">
+    <row r="910" spans="2:2" s="2" customFormat="1" ht="14.4">
       <c r="B910" s="1" t="s">
         <v>74</v>
       </c>
@@ -10912,48 +10912,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B236"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="3" width="2.875" style="5" customWidth="1"/>
+    <col min="1" max="3" width="2.8984375" style="5" customWidth="1"/>
     <col min="4" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="19.5">
+    <row r="1" spans="1:1" ht="19.8">
       <c r="A1" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="19.5">
+    <row r="34" spans="1:2" ht="19.8">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="19.5">
+    <row r="35" spans="1:2" ht="19.8">
       <c r="B35" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="19.5">
+    <row r="69" spans="2:2" ht="19.8">
       <c r="B69" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="2:2" ht="19.5">
+    <row r="102" spans="2:2" ht="19.8">
       <c r="B102" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="135" spans="2:2" ht="19.5">
+    <row r="135" spans="2:2" ht="19.8">
       <c r="B135" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="201" spans="2:2" ht="19.5">
+    <row r="201" spans="2:2" ht="19.8">
       <c r="B201" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="236" spans="1:1" ht="19.5">
+    <row r="236" spans="1:1" ht="19.8">
       <c r="A236" s="4" t="s">
         <v>82</v>
       </c>
@@ -10984,7 +10984,7 @@
   <dimension ref="A1:BB85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
-    <col min="1" max="112" width="2.75" style="36" customWidth="1"/>
+    <col min="1" max="112" width="2.69921875" style="36" customWidth="1"/>
     <col min="113" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
@@ -11733,16 +11733,16 @@
       <c r="AL13" s="54"/>
       <c r="AM13" s="54"/>
       <c r="AN13" s="54"/>
-      <c r="AO13" s="103"/>
-      <c r="AP13" s="104"/>
-      <c r="AQ13" s="104"/>
-      <c r="AR13" s="104"/>
-      <c r="AS13" s="104"/>
-      <c r="AT13" s="104"/>
-      <c r="AU13" s="104"/>
-      <c r="AV13" s="104"/>
-      <c r="AW13" s="104"/>
-      <c r="AX13" s="105"/>
+      <c r="AO13" s="112"/>
+      <c r="AP13" s="113"/>
+      <c r="AQ13" s="113"/>
+      <c r="AR13" s="113"/>
+      <c r="AS13" s="113"/>
+      <c r="AT13" s="113"/>
+      <c r="AU13" s="113"/>
+      <c r="AV13" s="113"/>
+      <c r="AW13" s="113"/>
+      <c r="AX13" s="114"/>
       <c r="AY13" s="9"/>
       <c r="AZ13" s="12"/>
       <c r="BA13" s="9"/>
@@ -11795,16 +11795,16 @@
       <c r="AL14" s="54"/>
       <c r="AM14" s="54"/>
       <c r="AN14" s="54"/>
-      <c r="AO14" s="103"/>
-      <c r="AP14" s="104"/>
-      <c r="AQ14" s="104"/>
-      <c r="AR14" s="104"/>
-      <c r="AS14" s="104"/>
-      <c r="AT14" s="104"/>
-      <c r="AU14" s="104"/>
-      <c r="AV14" s="104"/>
-      <c r="AW14" s="104"/>
-      <c r="AX14" s="105"/>
+      <c r="AO14" s="112"/>
+      <c r="AP14" s="113"/>
+      <c r="AQ14" s="113"/>
+      <c r="AR14" s="113"/>
+      <c r="AS14" s="113"/>
+      <c r="AT14" s="113"/>
+      <c r="AU14" s="113"/>
+      <c r="AV14" s="113"/>
+      <c r="AW14" s="113"/>
+      <c r="AX14" s="114"/>
       <c r="AY14" s="9"/>
       <c r="AZ14" s="12"/>
       <c r="BA14" s="9"/>
@@ -11857,16 +11857,16 @@
       <c r="AL15" s="54"/>
       <c r="AM15" s="54"/>
       <c r="AN15" s="54"/>
-      <c r="AO15" s="103"/>
-      <c r="AP15" s="104"/>
-      <c r="AQ15" s="104"/>
-      <c r="AR15" s="104"/>
-      <c r="AS15" s="104"/>
-      <c r="AT15" s="104"/>
-      <c r="AU15" s="104"/>
-      <c r="AV15" s="104"/>
-      <c r="AW15" s="104"/>
-      <c r="AX15" s="105"/>
+      <c r="AO15" s="112"/>
+      <c r="AP15" s="113"/>
+      <c r="AQ15" s="113"/>
+      <c r="AR15" s="113"/>
+      <c r="AS15" s="113"/>
+      <c r="AT15" s="113"/>
+      <c r="AU15" s="113"/>
+      <c r="AV15" s="113"/>
+      <c r="AW15" s="113"/>
+      <c r="AX15" s="114"/>
       <c r="AY15" s="9"/>
       <c r="AZ15" s="12"/>
       <c r="BA15" s="9"/>
@@ -11919,16 +11919,16 @@
       <c r="AL16" s="54"/>
       <c r="AM16" s="54"/>
       <c r="AN16" s="54"/>
-      <c r="AO16" s="103"/>
-      <c r="AP16" s="104"/>
-      <c r="AQ16" s="104"/>
-      <c r="AR16" s="104"/>
-      <c r="AS16" s="104"/>
-      <c r="AT16" s="104"/>
-      <c r="AU16" s="104"/>
-      <c r="AV16" s="104"/>
-      <c r="AW16" s="104"/>
-      <c r="AX16" s="105"/>
+      <c r="AO16" s="112"/>
+      <c r="AP16" s="113"/>
+      <c r="AQ16" s="113"/>
+      <c r="AR16" s="113"/>
+      <c r="AS16" s="113"/>
+      <c r="AT16" s="113"/>
+      <c r="AU16" s="113"/>
+      <c r="AV16" s="113"/>
+      <c r="AW16" s="113"/>
+      <c r="AX16" s="114"/>
       <c r="AY16" s="9"/>
       <c r="AZ16" s="12"/>
       <c r="BA16" s="9"/>
@@ -11981,16 +11981,16 @@
       <c r="AL17" s="54"/>
       <c r="AM17" s="54"/>
       <c r="AN17" s="54"/>
-      <c r="AO17" s="103"/>
-      <c r="AP17" s="104"/>
-      <c r="AQ17" s="104"/>
-      <c r="AR17" s="104"/>
-      <c r="AS17" s="104"/>
-      <c r="AT17" s="104"/>
-      <c r="AU17" s="104"/>
-      <c r="AV17" s="104"/>
-      <c r="AW17" s="104"/>
-      <c r="AX17" s="105"/>
+      <c r="AO17" s="112"/>
+      <c r="AP17" s="113"/>
+      <c r="AQ17" s="113"/>
+      <c r="AR17" s="113"/>
+      <c r="AS17" s="113"/>
+      <c r="AT17" s="113"/>
+      <c r="AU17" s="113"/>
+      <c r="AV17" s="113"/>
+      <c r="AW17" s="113"/>
+      <c r="AX17" s="114"/>
       <c r="AY17" s="9"/>
       <c r="AZ17" s="12"/>
       <c r="BA17" s="9"/>
@@ -12043,16 +12043,16 @@
       <c r="AL18" s="54"/>
       <c r="AM18" s="54"/>
       <c r="AN18" s="54"/>
-      <c r="AO18" s="103"/>
-      <c r="AP18" s="104"/>
-      <c r="AQ18" s="104"/>
-      <c r="AR18" s="104"/>
-      <c r="AS18" s="104"/>
-      <c r="AT18" s="104"/>
-      <c r="AU18" s="104"/>
-      <c r="AV18" s="104"/>
-      <c r="AW18" s="104"/>
-      <c r="AX18" s="105"/>
+      <c r="AO18" s="112"/>
+      <c r="AP18" s="113"/>
+      <c r="AQ18" s="113"/>
+      <c r="AR18" s="113"/>
+      <c r="AS18" s="113"/>
+      <c r="AT18" s="113"/>
+      <c r="AU18" s="113"/>
+      <c r="AV18" s="113"/>
+      <c r="AW18" s="113"/>
+      <c r="AX18" s="114"/>
       <c r="AY18" s="9"/>
       <c r="AZ18" s="12"/>
       <c r="BA18" s="9"/>
@@ -12105,16 +12105,16 @@
       <c r="AL19" s="54"/>
       <c r="AM19" s="54"/>
       <c r="AN19" s="54"/>
-      <c r="AO19" s="103"/>
-      <c r="AP19" s="104"/>
-      <c r="AQ19" s="104"/>
-      <c r="AR19" s="104"/>
-      <c r="AS19" s="104"/>
-      <c r="AT19" s="104"/>
-      <c r="AU19" s="104"/>
-      <c r="AV19" s="104"/>
-      <c r="AW19" s="104"/>
-      <c r="AX19" s="105"/>
+      <c r="AO19" s="112"/>
+      <c r="AP19" s="113"/>
+      <c r="AQ19" s="113"/>
+      <c r="AR19" s="113"/>
+      <c r="AS19" s="113"/>
+      <c r="AT19" s="113"/>
+      <c r="AU19" s="113"/>
+      <c r="AV19" s="113"/>
+      <c r="AW19" s="113"/>
+      <c r="AX19" s="114"/>
       <c r="AY19" s="9"/>
       <c r="AZ19" s="12"/>
       <c r="BA19" s="9"/>
@@ -12167,16 +12167,16 @@
       <c r="AL20" s="54"/>
       <c r="AM20" s="54"/>
       <c r="AN20" s="54"/>
-      <c r="AO20" s="103"/>
-      <c r="AP20" s="104"/>
-      <c r="AQ20" s="104"/>
-      <c r="AR20" s="104"/>
-      <c r="AS20" s="104"/>
-      <c r="AT20" s="104"/>
-      <c r="AU20" s="104"/>
-      <c r="AV20" s="104"/>
-      <c r="AW20" s="104"/>
-      <c r="AX20" s="105"/>
+      <c r="AO20" s="112"/>
+      <c r="AP20" s="113"/>
+      <c r="AQ20" s="113"/>
+      <c r="AR20" s="113"/>
+      <c r="AS20" s="113"/>
+      <c r="AT20" s="113"/>
+      <c r="AU20" s="113"/>
+      <c r="AV20" s="113"/>
+      <c r="AW20" s="113"/>
+      <c r="AX20" s="114"/>
       <c r="AY20" s="9"/>
       <c r="AZ20" s="12"/>
       <c r="BA20" s="9"/>
@@ -12808,16 +12808,16 @@
       <c r="AL31" s="54"/>
       <c r="AM31" s="54"/>
       <c r="AN31" s="54"/>
-      <c r="AO31" s="103"/>
-      <c r="AP31" s="104"/>
-      <c r="AQ31" s="104"/>
-      <c r="AR31" s="104"/>
-      <c r="AS31" s="104"/>
-      <c r="AT31" s="104"/>
-      <c r="AU31" s="104"/>
-      <c r="AV31" s="104"/>
-      <c r="AW31" s="104"/>
-      <c r="AX31" s="105"/>
+      <c r="AO31" s="112"/>
+      <c r="AP31" s="113"/>
+      <c r="AQ31" s="113"/>
+      <c r="AR31" s="113"/>
+      <c r="AS31" s="113"/>
+      <c r="AT31" s="113"/>
+      <c r="AU31" s="113"/>
+      <c r="AV31" s="113"/>
+      <c r="AW31" s="113"/>
+      <c r="AX31" s="114"/>
       <c r="AY31" s="9"/>
       <c r="AZ31" s="12"/>
       <c r="BA31" s="9"/>
@@ -12870,16 +12870,16 @@
       <c r="AL32" s="54"/>
       <c r="AM32" s="54"/>
       <c r="AN32" s="54"/>
-      <c r="AO32" s="103"/>
-      <c r="AP32" s="104"/>
-      <c r="AQ32" s="104"/>
-      <c r="AR32" s="104"/>
-      <c r="AS32" s="104"/>
-      <c r="AT32" s="104"/>
-      <c r="AU32" s="104"/>
-      <c r="AV32" s="104"/>
-      <c r="AW32" s="104"/>
-      <c r="AX32" s="105"/>
+      <c r="AO32" s="112"/>
+      <c r="AP32" s="113"/>
+      <c r="AQ32" s="113"/>
+      <c r="AR32" s="113"/>
+      <c r="AS32" s="113"/>
+      <c r="AT32" s="113"/>
+      <c r="AU32" s="113"/>
+      <c r="AV32" s="113"/>
+      <c r="AW32" s="113"/>
+      <c r="AX32" s="114"/>
       <c r="AY32" s="9"/>
       <c r="AZ32" s="12"/>
       <c r="BA32" s="9"/>
@@ -12932,16 +12932,16 @@
       <c r="AL33" s="54"/>
       <c r="AM33" s="54"/>
       <c r="AN33" s="54"/>
-      <c r="AO33" s="103"/>
-      <c r="AP33" s="104"/>
-      <c r="AQ33" s="104"/>
-      <c r="AR33" s="104"/>
-      <c r="AS33" s="104"/>
-      <c r="AT33" s="104"/>
-      <c r="AU33" s="104"/>
-      <c r="AV33" s="104"/>
-      <c r="AW33" s="104"/>
-      <c r="AX33" s="105"/>
+      <c r="AO33" s="112"/>
+      <c r="AP33" s="113"/>
+      <c r="AQ33" s="113"/>
+      <c r="AR33" s="113"/>
+      <c r="AS33" s="113"/>
+      <c r="AT33" s="113"/>
+      <c r="AU33" s="113"/>
+      <c r="AV33" s="113"/>
+      <c r="AW33" s="113"/>
+      <c r="AX33" s="114"/>
       <c r="AY33" s="9"/>
       <c r="AZ33" s="12"/>
       <c r="BA33" s="9"/>
@@ -12994,16 +12994,16 @@
       <c r="AL34" s="54"/>
       <c r="AM34" s="54"/>
       <c r="AN34" s="54"/>
-      <c r="AO34" s="103"/>
-      <c r="AP34" s="104"/>
-      <c r="AQ34" s="104"/>
-      <c r="AR34" s="104"/>
-      <c r="AS34" s="104"/>
-      <c r="AT34" s="104"/>
-      <c r="AU34" s="104"/>
-      <c r="AV34" s="104"/>
-      <c r="AW34" s="104"/>
-      <c r="AX34" s="105"/>
+      <c r="AO34" s="112"/>
+      <c r="AP34" s="113"/>
+      <c r="AQ34" s="113"/>
+      <c r="AR34" s="113"/>
+      <c r="AS34" s="113"/>
+      <c r="AT34" s="113"/>
+      <c r="AU34" s="113"/>
+      <c r="AV34" s="113"/>
+      <c r="AW34" s="113"/>
+      <c r="AX34" s="114"/>
       <c r="AY34" s="9"/>
       <c r="AZ34" s="12"/>
       <c r="BA34" s="9"/>
@@ -14184,53 +14184,53 @@
         <v>154</v>
       </c>
       <c r="E55" s="9"/>
-      <c r="F55" s="106" t="s">
+      <c r="F55" s="111" t="s">
         <v>155</v>
       </c>
-      <c r="G55" s="106"/>
-      <c r="H55" s="106"/>
-      <c r="I55" s="106"/>
-      <c r="J55" s="106"/>
-      <c r="K55" s="106"/>
-      <c r="L55" s="106"/>
-      <c r="M55" s="106"/>
-      <c r="N55" s="106"/>
-      <c r="O55" s="106"/>
-      <c r="P55" s="106"/>
-      <c r="Q55" s="106"/>
-      <c r="R55" s="106"/>
-      <c r="S55" s="106"/>
-      <c r="T55" s="106"/>
-      <c r="U55" s="106"/>
-      <c r="V55" s="106"/>
-      <c r="W55" s="106"/>
-      <c r="X55" s="106"/>
-      <c r="Y55" s="106"/>
-      <c r="Z55" s="106"/>
-      <c r="AA55" s="106"/>
-      <c r="AB55" s="106"/>
-      <c r="AC55" s="106"/>
-      <c r="AD55" s="106"/>
-      <c r="AE55" s="106"/>
-      <c r="AF55" s="106"/>
-      <c r="AG55" s="106"/>
-      <c r="AH55" s="106"/>
-      <c r="AI55" s="106"/>
-      <c r="AJ55" s="106"/>
-      <c r="AK55" s="106"/>
-      <c r="AL55" s="106"/>
-      <c r="AM55" s="106"/>
-      <c r="AN55" s="106"/>
-      <c r="AO55" s="106"/>
-      <c r="AP55" s="106"/>
-      <c r="AQ55" s="106"/>
-      <c r="AR55" s="106"/>
-      <c r="AS55" s="106"/>
-      <c r="AT55" s="106"/>
-      <c r="AU55" s="106"/>
-      <c r="AV55" s="106"/>
-      <c r="AW55" s="106"/>
-      <c r="AX55" s="106"/>
+      <c r="G55" s="111"/>
+      <c r="H55" s="111"/>
+      <c r="I55" s="111"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="111"/>
+      <c r="L55" s="111"/>
+      <c r="M55" s="111"/>
+      <c r="N55" s="111"/>
+      <c r="O55" s="111"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="111"/>
+      <c r="S55" s="111"/>
+      <c r="T55" s="111"/>
+      <c r="U55" s="111"/>
+      <c r="V55" s="111"/>
+      <c r="W55" s="111"/>
+      <c r="X55" s="111"/>
+      <c r="Y55" s="111"/>
+      <c r="Z55" s="111"/>
+      <c r="AA55" s="111"/>
+      <c r="AB55" s="111"/>
+      <c r="AC55" s="111"/>
+      <c r="AD55" s="111"/>
+      <c r="AE55" s="111"/>
+      <c r="AF55" s="111"/>
+      <c r="AG55" s="111"/>
+      <c r="AH55" s="111"/>
+      <c r="AI55" s="111"/>
+      <c r="AJ55" s="111"/>
+      <c r="AK55" s="111"/>
+      <c r="AL55" s="111"/>
+      <c r="AM55" s="111"/>
+      <c r="AN55" s="111"/>
+      <c r="AO55" s="111"/>
+      <c r="AP55" s="111"/>
+      <c r="AQ55" s="111"/>
+      <c r="AR55" s="111"/>
+      <c r="AS55" s="111"/>
+      <c r="AT55" s="111"/>
+      <c r="AU55" s="111"/>
+      <c r="AV55" s="111"/>
+      <c r="AW55" s="111"/>
+      <c r="AX55" s="111"/>
       <c r="AY55" s="9"/>
       <c r="AZ55" s="12"/>
       <c r="BA55" s="9"/>
@@ -14242,51 +14242,51 @@
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="106"/>
-      <c r="G56" s="106"/>
-      <c r="H56" s="106"/>
-      <c r="I56" s="106"/>
-      <c r="J56" s="106"/>
-      <c r="K56" s="106"/>
-      <c r="L56" s="106"/>
-      <c r="M56" s="106"/>
-      <c r="N56" s="106"/>
-      <c r="O56" s="106"/>
-      <c r="P56" s="106"/>
-      <c r="Q56" s="106"/>
-      <c r="R56" s="106"/>
-      <c r="S56" s="106"/>
-      <c r="T56" s="106"/>
-      <c r="U56" s="106"/>
-      <c r="V56" s="106"/>
-      <c r="W56" s="106"/>
-      <c r="X56" s="106"/>
-      <c r="Y56" s="106"/>
-      <c r="Z56" s="106"/>
-      <c r="AA56" s="106"/>
-      <c r="AB56" s="106"/>
-      <c r="AC56" s="106"/>
-      <c r="AD56" s="106"/>
-      <c r="AE56" s="106"/>
-      <c r="AF56" s="106"/>
-      <c r="AG56" s="106"/>
-      <c r="AH56" s="106"/>
-      <c r="AI56" s="106"/>
-      <c r="AJ56" s="106"/>
-      <c r="AK56" s="106"/>
-      <c r="AL56" s="106"/>
-      <c r="AM56" s="106"/>
-      <c r="AN56" s="106"/>
-      <c r="AO56" s="106"/>
-      <c r="AP56" s="106"/>
-      <c r="AQ56" s="106"/>
-      <c r="AR56" s="106"/>
-      <c r="AS56" s="106"/>
-      <c r="AT56" s="106"/>
-      <c r="AU56" s="106"/>
-      <c r="AV56" s="106"/>
-      <c r="AW56" s="106"/>
-      <c r="AX56" s="106"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="111"/>
+      <c r="N56" s="111"/>
+      <c r="O56" s="111"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="111"/>
+      <c r="S56" s="111"/>
+      <c r="T56" s="111"/>
+      <c r="U56" s="111"/>
+      <c r="V56" s="111"/>
+      <c r="W56" s="111"/>
+      <c r="X56" s="111"/>
+      <c r="Y56" s="111"/>
+      <c r="Z56" s="111"/>
+      <c r="AA56" s="111"/>
+      <c r="AB56" s="111"/>
+      <c r="AC56" s="111"/>
+      <c r="AD56" s="111"/>
+      <c r="AE56" s="111"/>
+      <c r="AF56" s="111"/>
+      <c r="AG56" s="111"/>
+      <c r="AH56" s="111"/>
+      <c r="AI56" s="111"/>
+      <c r="AJ56" s="111"/>
+      <c r="AK56" s="111"/>
+      <c r="AL56" s="111"/>
+      <c r="AM56" s="111"/>
+      <c r="AN56" s="111"/>
+      <c r="AO56" s="111"/>
+      <c r="AP56" s="111"/>
+      <c r="AQ56" s="111"/>
+      <c r="AR56" s="111"/>
+      <c r="AS56" s="111"/>
+      <c r="AT56" s="111"/>
+      <c r="AU56" s="111"/>
+      <c r="AV56" s="111"/>
+      <c r="AW56" s="111"/>
+      <c r="AX56" s="111"/>
       <c r="AY56" s="9"/>
       <c r="AZ56" s="12"/>
       <c r="BA56" s="9"/>
@@ -14298,51 +14298,51 @@
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
-      <c r="F57" s="106"/>
-      <c r="G57" s="106"/>
-      <c r="H57" s="106"/>
-      <c r="I57" s="106"/>
-      <c r="J57" s="106"/>
-      <c r="K57" s="106"/>
-      <c r="L57" s="106"/>
-      <c r="M57" s="106"/>
-      <c r="N57" s="106"/>
-      <c r="O57" s="106"/>
-      <c r="P57" s="106"/>
-      <c r="Q57" s="106"/>
-      <c r="R57" s="106"/>
-      <c r="S57" s="106"/>
-      <c r="T57" s="106"/>
-      <c r="U57" s="106"/>
-      <c r="V57" s="106"/>
-      <c r="W57" s="106"/>
-      <c r="X57" s="106"/>
-      <c r="Y57" s="106"/>
-      <c r="Z57" s="106"/>
-      <c r="AA57" s="106"/>
-      <c r="AB57" s="106"/>
-      <c r="AC57" s="106"/>
-      <c r="AD57" s="106"/>
-      <c r="AE57" s="106"/>
-      <c r="AF57" s="106"/>
-      <c r="AG57" s="106"/>
-      <c r="AH57" s="106"/>
-      <c r="AI57" s="106"/>
-      <c r="AJ57" s="106"/>
-      <c r="AK57" s="106"/>
-      <c r="AL57" s="106"/>
-      <c r="AM57" s="106"/>
-      <c r="AN57" s="106"/>
-      <c r="AO57" s="106"/>
-      <c r="AP57" s="106"/>
-      <c r="AQ57" s="106"/>
-      <c r="AR57" s="106"/>
-      <c r="AS57" s="106"/>
-      <c r="AT57" s="106"/>
-      <c r="AU57" s="106"/>
-      <c r="AV57" s="106"/>
-      <c r="AW57" s="106"/>
-      <c r="AX57" s="106"/>
+      <c r="F57" s="111"/>
+      <c r="G57" s="111"/>
+      <c r="H57" s="111"/>
+      <c r="I57" s="111"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="111"/>
+      <c r="L57" s="111"/>
+      <c r="M57" s="111"/>
+      <c r="N57" s="111"/>
+      <c r="O57" s="111"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="111"/>
+      <c r="S57" s="111"/>
+      <c r="T57" s="111"/>
+      <c r="U57" s="111"/>
+      <c r="V57" s="111"/>
+      <c r="W57" s="111"/>
+      <c r="X57" s="111"/>
+      <c r="Y57" s="111"/>
+      <c r="Z57" s="111"/>
+      <c r="AA57" s="111"/>
+      <c r="AB57" s="111"/>
+      <c r="AC57" s="111"/>
+      <c r="AD57" s="111"/>
+      <c r="AE57" s="111"/>
+      <c r="AF57" s="111"/>
+      <c r="AG57" s="111"/>
+      <c r="AH57" s="111"/>
+      <c r="AI57" s="111"/>
+      <c r="AJ57" s="111"/>
+      <c r="AK57" s="111"/>
+      <c r="AL57" s="111"/>
+      <c r="AM57" s="111"/>
+      <c r="AN57" s="111"/>
+      <c r="AO57" s="111"/>
+      <c r="AP57" s="111"/>
+      <c r="AQ57" s="111"/>
+      <c r="AR57" s="111"/>
+      <c r="AS57" s="111"/>
+      <c r="AT57" s="111"/>
+      <c r="AU57" s="111"/>
+      <c r="AV57" s="111"/>
+      <c r="AW57" s="111"/>
+      <c r="AX57" s="111"/>
       <c r="AY57" s="9"/>
       <c r="AZ57" s="12"/>
       <c r="BA57" s="9"/>
@@ -14353,51 +14353,51 @@
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
       <c r="E58" s="9"/>
-      <c r="F58" s="106"/>
-      <c r="G58" s="106"/>
-      <c r="H58" s="106"/>
-      <c r="I58" s="106"/>
-      <c r="J58" s="106"/>
-      <c r="K58" s="106"/>
-      <c r="L58" s="106"/>
-      <c r="M58" s="106"/>
-      <c r="N58" s="106"/>
-      <c r="O58" s="106"/>
-      <c r="P58" s="106"/>
-      <c r="Q58" s="106"/>
-      <c r="R58" s="106"/>
-      <c r="S58" s="106"/>
-      <c r="T58" s="106"/>
-      <c r="U58" s="106"/>
-      <c r="V58" s="106"/>
-      <c r="W58" s="106"/>
-      <c r="X58" s="106"/>
-      <c r="Y58" s="106"/>
-      <c r="Z58" s="106"/>
-      <c r="AA58" s="106"/>
-      <c r="AB58" s="106"/>
-      <c r="AC58" s="106"/>
-      <c r="AD58" s="106"/>
-      <c r="AE58" s="106"/>
-      <c r="AF58" s="106"/>
-      <c r="AG58" s="106"/>
-      <c r="AH58" s="106"/>
-      <c r="AI58" s="106"/>
-      <c r="AJ58" s="106"/>
-      <c r="AK58" s="106"/>
-      <c r="AL58" s="106"/>
-      <c r="AM58" s="106"/>
-      <c r="AN58" s="106"/>
-      <c r="AO58" s="106"/>
-      <c r="AP58" s="106"/>
-      <c r="AQ58" s="106"/>
-      <c r="AR58" s="106"/>
-      <c r="AS58" s="106"/>
-      <c r="AT58" s="106"/>
-      <c r="AU58" s="106"/>
-      <c r="AV58" s="106"/>
-      <c r="AW58" s="106"/>
-      <c r="AX58" s="106"/>
+      <c r="F58" s="111"/>
+      <c r="G58" s="111"/>
+      <c r="H58" s="111"/>
+      <c r="I58" s="111"/>
+      <c r="J58" s="111"/>
+      <c r="K58" s="111"/>
+      <c r="L58" s="111"/>
+      <c r="M58" s="111"/>
+      <c r="N58" s="111"/>
+      <c r="O58" s="111"/>
+      <c r="P58" s="111"/>
+      <c r="Q58" s="111"/>
+      <c r="R58" s="111"/>
+      <c r="S58" s="111"/>
+      <c r="T58" s="111"/>
+      <c r="U58" s="111"/>
+      <c r="V58" s="111"/>
+      <c r="W58" s="111"/>
+      <c r="X58" s="111"/>
+      <c r="Y58" s="111"/>
+      <c r="Z58" s="111"/>
+      <c r="AA58" s="111"/>
+      <c r="AB58" s="111"/>
+      <c r="AC58" s="111"/>
+      <c r="AD58" s="111"/>
+      <c r="AE58" s="111"/>
+      <c r="AF58" s="111"/>
+      <c r="AG58" s="111"/>
+      <c r="AH58" s="111"/>
+      <c r="AI58" s="111"/>
+      <c r="AJ58" s="111"/>
+      <c r="AK58" s="111"/>
+      <c r="AL58" s="111"/>
+      <c r="AM58" s="111"/>
+      <c r="AN58" s="111"/>
+      <c r="AO58" s="111"/>
+      <c r="AP58" s="111"/>
+      <c r="AQ58" s="111"/>
+      <c r="AR58" s="111"/>
+      <c r="AS58" s="111"/>
+      <c r="AT58" s="111"/>
+      <c r="AU58" s="111"/>
+      <c r="AV58" s="111"/>
+      <c r="AW58" s="111"/>
+      <c r="AX58" s="111"/>
       <c r="AY58" s="9"/>
       <c r="AZ58" s="12"/>
       <c r="BA58" s="9"/>
@@ -15963,6 +15963,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="AO18:AX18"/>
+    <mergeCell ref="AO13:AX13"/>
+    <mergeCell ref="AO14:AX14"/>
+    <mergeCell ref="AO15:AX15"/>
+    <mergeCell ref="AO16:AX16"/>
+    <mergeCell ref="AO17:AX17"/>
     <mergeCell ref="F55:AX58"/>
     <mergeCell ref="AO19:AX19"/>
     <mergeCell ref="AO20:AX20"/>
@@ -15970,19 +15976,13 @@
     <mergeCell ref="AO32:AX32"/>
     <mergeCell ref="AO33:AX33"/>
     <mergeCell ref="AO34:AX34"/>
-    <mergeCell ref="AO18:AX18"/>
-    <mergeCell ref="AO13:AX13"/>
-    <mergeCell ref="AO14:AX14"/>
-    <mergeCell ref="AO15:AX15"/>
-    <mergeCell ref="AO16:AX16"/>
-    <mergeCell ref="AO17:AX17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="Q32" r:id="rId1" xr:uid="{65B5CDC5-688D-471B-880B-11288D87ADD8}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="58" fitToHeight="0" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId2"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P/&amp;N&amp;R&amp;A</oddFooter>
   </headerFooter>
@@ -15992,9 +15992,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A0FBB4-DC83-47EE-870B-E93519FAAA6C}">
   <dimension ref="B2:N25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="3" width="3.625" customWidth="1"/>
+    <col min="1" max="3" width="3.59765625" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
